--- a/outputs/35742.xlsx
+++ b/outputs/35742.xlsx
@@ -376,135 +376,135 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/outputs/35742.xlsx
+++ b/outputs/35742.xlsx
@@ -965,7 +965,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="23" t="n">
-        <f aca="false">SUM(IFERROR(VALUE(F4),0),IFERROR(VALUE(H4),0),IFERROR(VALUE(J4),0),IFERROR(VALUE(L4),0),IFERROR(VALUE(N4),0))</f>
+        <f aca="false">IF(F4="",0,F4)+IF(H4="",0,H4)+IF(J4="",0,J4)+IF(L4="",0,L4)+IF(N4="",0,N4)</f>
         <v>17</v>
       </c>
       <c r="P4" s="23"/>
@@ -1032,7 +1032,7 @@
         <v/>
       </c>
       <c r="O5" s="4" t="n">
-        <f aca="false">SUM(IFERROR(VALUE(F5),0),IFERROR(VALUE(H5),0),IFERROR(VALUE(J5),0),IFERROR(VALUE(L5),0),IFERROR(VALUE(N5),0))</f>
+        <f aca="false">IF(F5="",0,F5)+IF(H5="",0,H5)+IF(J5="",0,J5)+IF(L5="",0,L5)+IF(N5="",0,N5)</f>
         <v>7</v>
       </c>
       <c r="R5" s="24"/>
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="O6" s="4" t="n">
-        <f aca="false">SUM(IFERROR(VALUE(F6),0),IFERROR(VALUE(H6),0),IFERROR(VALUE(J6),0),IFERROR(VALUE(L6),0),IFERROR(VALUE(N6),0))</f>
+        <f aca="false">IF(F6="",0,F6)+IF(H6="",0,H6)+IF(J6="",0,J6)+IF(L6="",0,L6)+IF(N6="",0,N6)</f>
         <v>9</v>
       </c>
       <c r="R6" s="24"/>
@@ -1165,7 +1165,7 @@
         <v/>
       </c>
       <c r="O7" s="4" t="n">
-        <f aca="false">SUM(IFERROR(VALUE(F7),0),IFERROR(VALUE(H7),0),IFERROR(VALUE(J7),0),IFERROR(VALUE(L7),0),IFERROR(VALUE(N7),0))</f>
+        <f aca="false">IF(F7="",0,F7)+IF(H7="",0,H7)+IF(J7="",0,J7)+IF(L7="",0,L7)+IF(N7="",0,N7)</f>
         <v>6</v>
       </c>
       <c r="P7" s="33"/>
